--- a/AAAGameData/Languages/ChineseTraditional.xlsx
+++ b/AAAGameData/Languages/ChineseTraditional.xlsx
@@ -62,12 +62,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>BRAKE</t>
   </si>
   <si>
-    <t>刹車</t>
+    <t>煞車</t>
   </si>
   <si>
     <t>ENGINE</t>
@@ -79,12 +79,15 @@
     <t>Failed</t>
   </si>
   <si>
-    <t/>
+    <t>遊戲失敗</t>
   </si>
   <si>
     <t>GameOverUIForm.Back</t>
   </si>
   <si>
+    <t>返回</t>
+  </si>
+  <si>
     <t>Level.DisplayName1</t>
   </si>
   <si>
@@ -124,7 +127,7 @@
     <t>Nothing</t>
   </si>
   <si>
-    <t>未實現</t>
+    <t>未實作</t>
   </si>
   <si>
     <t>OFF</t>
@@ -148,19 +151,19 @@
     <t>RatingDialog.Description</t>
   </si>
   <si>
-    <t>喜歡這款遊戲嗎？ \n請給個5星好評吧！</t>
+    <t>喜歡這款遊戲嗎?\n請給個5星好評吧!</t>
   </si>
   <si>
     <t>RatingDialog.HighRatingTips</t>
   </si>
   <si>
-    <t>感謝您的肯定！ 我們將再接再厲！</t>
+    <t>感謝您的肯定! 我們將再接再厲!</t>
   </si>
   <si>
     <t>RatingDialog.LowRatingTips</t>
   </si>
   <si>
-    <t>感謝您的評估，我們盡力完善優化！</t>
+    <t>感謝您的評價,我們盡力完善優化!</t>
   </si>
   <si>
     <t>RatingDialog.RateTxt</t>
@@ -169,10 +172,22 @@
     <t>評星</t>
   </si>
   <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>商店</t>
+  </si>
+  <si>
+    <t>STEERING</t>
+  </si>
+  <si>
+    <t>駕駛</t>
+  </si>
+  <si>
     <t>Settings.Help</t>
   </si>
   <si>
-    <t>幫助反饋</t>
+    <t>幫助/回饋</t>
   </si>
   <si>
     <t>Settings.Language</t>
@@ -190,7 +205,7 @@
     <t>Settings.Privacy</t>
   </si>
   <si>
-    <t>隱私協定</t>
+    <t>隱私協議</t>
   </si>
   <si>
     <t>Settings.Rating</t>
@@ -217,18 +232,6 @@
     <t>震動</t>
   </si>
   <si>
-    <t>SHOP</t>
-  </si>
-  <si>
-    <t>商店</t>
-  </si>
-  <si>
-    <t>STEERING</t>
-  </si>
-  <si>
-    <t>駕駛</t>
-  </si>
-  <si>
     <t>TermsOfService</t>
   </si>
   <si>
@@ -242,6 +245,9 @@
   </si>
   <si>
     <t>Victory</t>
+  </si>
+  <si>
+    <t>遊戲勝利</t>
   </si>
 </sst>
 </file>
@@ -423,6 +429,130 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -4468,7 +4598,7 @@
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
     <col min="2" max="2" width="25.4074859619141" customWidth="1"/>
-    <col min="3" max="3" width="42.2229309082031" customWidth="1"/>
+    <col min="3" max="3" width="38.6902858189174" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4504,250 +4634,250 @@
         <v>6</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1"/>
       <c r="B10" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1"/>
       <c r="B11" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1"/>
       <c r="B12" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1"/>
       <c r="B13" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1"/>
       <c r="B14" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1"/>
       <c r="B15" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1"/>
       <c r="B16" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1"/>
       <c r="B17" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1"/>
       <c r="B18" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1"/>
       <c r="B19" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1"/>
       <c r="B20" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1"/>
       <c r="B21" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1"/>
       <c r="B22" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1"/>
       <c r="B23" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1"/>
       <c r="B24" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1"/>
       <c r="B25" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1"/>
       <c r="B26" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1"/>
       <c r="B27" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1"/>
       <c r="B28" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1"/>
       <c r="B29" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1"/>
       <c r="B30" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1"/>
       <c r="B31" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -4762,7 +4892,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId273" name="A1">
+            <control shapeId="1056" r:id="rId303" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4784,7 +4914,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId274" name="A2">
+            <control shapeId="1057" r:id="rId304" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4806,7 +4936,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId275" name="A3">
+            <control shapeId="1058" r:id="rId305" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4828,7 +4958,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId276" name="A4">
+            <control shapeId="1059" r:id="rId306" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4850,7 +4980,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId277" name="A5">
+            <control shapeId="1060" r:id="rId307" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4872,7 +5002,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId278" name="A6">
+            <control shapeId="1061" r:id="rId308" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4894,7 +5024,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId279" name="A7">
+            <control shapeId="1062" r:id="rId309" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4916,7 +5046,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId280" name="A8">
+            <control shapeId="1063" r:id="rId310" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4938,7 +5068,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId281" name="A9">
+            <control shapeId="1064" r:id="rId311" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4960,7 +5090,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId282" name="A10">
+            <control shapeId="1065" r:id="rId312" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4982,7 +5112,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId283" name="A11">
+            <control shapeId="1066" r:id="rId313" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5004,7 +5134,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId284" name="A12">
+            <control shapeId="1067" r:id="rId314" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5026,7 +5156,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId285" name="A13">
+            <control shapeId="1068" r:id="rId315" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5048,7 +5178,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId286" name="A14">
+            <control shapeId="1069" r:id="rId316" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5070,7 +5200,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId287" name="A15">
+            <control shapeId="1070" r:id="rId317" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5092,7 +5222,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId288" name="A16">
+            <control shapeId="1071" r:id="rId318" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5114,7 +5244,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId289" name="A17">
+            <control shapeId="1072" r:id="rId319" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5136,7 +5266,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId290" name="A18">
+            <control shapeId="1073" r:id="rId320" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5158,7 +5288,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId291" name="A19">
+            <control shapeId="1074" r:id="rId321" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5180,7 +5310,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId292" name="A20">
+            <control shapeId="1075" r:id="rId322" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5202,7 +5332,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId293" name="A21">
+            <control shapeId="1076" r:id="rId323" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5224,7 +5354,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId294" name="A22">
+            <control shapeId="1077" r:id="rId324" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5246,7 +5376,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId295" name="A23">
+            <control shapeId="1078" r:id="rId325" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5268,7 +5398,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId296" name="A24">
+            <control shapeId="1079" r:id="rId326" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5290,7 +5420,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId297" name="A25">
+            <control shapeId="1080" r:id="rId327" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5312,7 +5442,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId298" name="A26">
+            <control shapeId="1081" r:id="rId328" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5334,7 +5464,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId299" name="A27">
+            <control shapeId="1082" r:id="rId329" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5356,7 +5486,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId300" name="A28">
+            <control shapeId="1083" r:id="rId330" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5378,7 +5508,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId301" name="A29">
+            <control shapeId="1084" r:id="rId331" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5400,7 +5530,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId302" name="A30">
+            <control shapeId="1085" r:id="rId332" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5422,7 +5552,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId303" name="A31">
+            <control shapeId="1086" r:id="rId333" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
